--- a/artfynd/A 8909-2025 artfynd.xlsx
+++ b/artfynd/A 8909-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>65391507</v>
+        <v>65391456</v>
       </c>
       <c r="B2" t="n">
-        <v>107845</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111019</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>407164.3688017498</v>
+        <v>407134</v>
       </c>
       <c r="R2" t="n">
-        <v>6598108.344005606</v>
+        <v>6598101</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +746,9 @@
           <t>2017-05-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-05-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,15 +775,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>65391456</v>
+        <v>65391507</v>
       </c>
       <c r="B3" t="n">
-        <v>107845</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111019</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -833,10 +813,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>407134.1767228218</v>
+        <v>407164</v>
       </c>
       <c r="R3" t="n">
-        <v>6598100.96499751</v>
+        <v>6598108</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,19 +846,9 @@
           <t>2017-05-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-05-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,12 +878,7 @@
         <v>68625430</v>
       </c>
       <c r="B4" t="n">
-        <v>107845</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>111019</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,10 +910,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>407149.5144200959</v>
+        <v>407150</v>
       </c>
       <c r="R4" t="n">
-        <v>6598104.140747098</v>
+        <v>6598104</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,19 +948,9 @@
           <t>2017-05-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-05-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
